--- a/2viestiyhteys.xlsx
+++ b/2viestiyhteys.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206DC0E8-E6D9-469D-941D-17A570A5A8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="32205" yWindow="3750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32205" yWindow="3750" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>I</t>
   </si>
@@ -88,12 +87,30 @@
   </si>
   <si>
     <t>8kV</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>1/(2*pi*R*C)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -405,9 +422,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:D16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -552,6 +572,49 @@
         <v>5</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <f>100*10^-9</f>
+        <v>1.0000000000000001E-7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>10000</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <f>1/(2*3.1415*B20*B19)</f>
+        <v>159.15963711602737</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2viestiyhteys.xlsx
+++ b/2viestiyhteys.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CFB94A-BE37-4D9A-9008-A81E6617A002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32205" yWindow="3750" windowWidth="21600" windowHeight="11295"/>
+    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>I</t>
   </si>
@@ -98,21 +99,47 @@
     <t>F</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Hz</t>
   </si>
   <si>
-    <t>1/(2*pi*R*C)</t>
+    <t>Komponentti</t>
+  </si>
+  <si>
+    <t>Arvo/Kaava</t>
+  </si>
+  <si>
+    <t>Lähetin</t>
+  </si>
+  <si>
+    <t>Vastaanotin</t>
+  </si>
+  <si>
+    <t>Alipäästösuodattimen rajataajuus</t>
+  </si>
+  <si>
+    <t>1/(2*pi*R3*C)</t>
+  </si>
+  <si>
+    <t>Yksikkö</t>
+  </si>
+  <si>
+    <t>Lasku</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -128,7 +155,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -136,13 +163,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -158,6 +275,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>168519</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>102576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>109904</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>75499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6FD5B88-34BC-F0C9-2C89-F7A0BE139FA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3055327" y="293076"/>
+          <a:ext cx="4198327" cy="3401923"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>439616</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>7327</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>204558</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>121696</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50F67D9F-6570-9760-B120-339D6F0AC236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2718289" y="4007827"/>
+          <a:ext cx="981212" cy="495369"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -422,200 +632,247 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:D21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C5" s="6">
         <v>3</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
+      <c r="C6" s="6">
         <f>20*10^(-3)</f>
         <v>0.02</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
-        <f>C4/C5</f>
+      <c r="C8" s="9">
+        <f>C5/C6</f>
         <v>150</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C9">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6">
         <f>20*10^(-3)</f>
         <v>0.02</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C10">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D13" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C11">
-        <f>C10/C9</f>
+      <c r="C14" s="9">
+        <f>C13/C12</f>
         <v>250</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D14" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14">
+      <c r="C17" s="6">
         <v>8000</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D17" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="1">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6">
         <f>8*10^(-1)</f>
         <v>0.8</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D18" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B19" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="1">
-        <f>C14/C15</f>
+      <c r="C19" s="9">
+        <f>C17/C18</f>
         <v>10000</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D19" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B19">
+      <c r="B22" s="3">
         <f>100*10^-9</f>
         <v>1.0000000000000001E-7</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10000</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="9">
+        <f>1/(2*3.1415*B23*B22)</f>
+        <v>159.15963711602737</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="B20">
-        <v>10000</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21">
-        <f>1/(2*3.1415*B20*B19)</f>
-        <v>159.15963711602737</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>